--- a/PruebasClaves.xlsx
+++ b/PruebasClaves.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\emilio\Documents\ficheros\cursos\InfromaticaBurgos\Q5\23_ValidacionYPruebas\codigo\practica1\TPMP-bpg-eca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Balder cron\Documents\GitHub\TPMP-bpg-eca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475DFE26-8E14-4F5D-AA7E-45531C25C56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB80D302-4111-435B-8C07-8039C33D80B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37710" yWindow="-705" windowWidth="24210" windowHeight="13710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -66,58 +66,67 @@
     <t>Evaluar contraseña nula</t>
   </si>
   <si>
-    <t>Evaluar contraseña espacios</t>
-  </si>
-  <si>
     <t>null</t>
   </si>
   <si>
-    <t>FALSO</t>
-  </si>
-  <si>
-    <t>Evaluar contraseña correcta</t>
-  </si>
-  <si>
-    <t>P@ssw0rd</t>
-  </si>
-  <si>
-    <t>VERDADERO</t>
-  </si>
-  <si>
-    <t>Evaluar contraseña sin caracter especial</t>
-  </si>
-  <si>
-    <t>Passw0rd</t>
-  </si>
-  <si>
-    <t>P@ssw0r</t>
-  </si>
-  <si>
-    <t>P@SSW0RD</t>
-  </si>
-  <si>
-    <t>P@ssword</t>
-  </si>
-  <si>
-    <t>Evaluar contrraseña sin longitud minima</t>
-  </si>
-  <si>
-    <t>Evaluar contrraseña sin mayuscula</t>
-  </si>
-  <si>
-    <t>Evaluar contrraseña sin minuscula</t>
-  </si>
-  <si>
-    <t>Evaluar contrraseña sin numero</t>
-  </si>
-  <si>
-    <t>p@ssw0rd</t>
-  </si>
-  <si>
     <t>lineas</t>
   </si>
   <si>
-    <t xml:space="preserve">     </t>
+    <t>Evaluar contraseña con solo espacios</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña de 11 caracteres</t>
+  </si>
+  <si>
+    <t>ClaveSegu1!</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña sin mayúsculas</t>
+  </si>
+  <si>
+    <t>clavesegur1!</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña sin minúsculas</t>
+  </si>
+  <si>
+    <t>CLAVESEGUR1!</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña sin números</t>
+  </si>
+  <si>
+    <t>ClaveSegura!</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña sin carácter especial</t>
+  </si>
+  <si>
+    <t>ClaveSegur12</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña válida de 12 caracteres</t>
+  </si>
+  <si>
+    <t>ClaveSegur1!</t>
+  </si>
+  <si>
+    <t>CP-09</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña vacía</t>
+  </si>
+  <si>
+    <t>CP-10</t>
+  </si>
+  <si>
+    <t>Evaluar contraseña válida de 13 caracteres</t>
+  </si>
+  <si>
+    <t>ClaveSegur12!</t>
+  </si>
+  <si>
+    <t>""</t>
   </si>
 </sst>
 </file>
@@ -455,11 +464,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -478,7 +487,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -489,14 +498,14 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C2 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("null"));</v>
+        <f>"Assert.IsFalse(ServicioContrasenas.EsValida(null!));"</f>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida(null!));</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -504,17 +513,18 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C3 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("     "));</v>
+      <c r="C3" t="str">
+        <f>REPT(" ",12)</f>
+        <v xml:space="preserve">            </v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="str">
+        <f>"Assert.IsFalse(ServicioContrasenas.EsValida("""&amp;C3&amp;"""));"</f>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida("            "));</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -522,17 +532,17 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C4 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("P@ssw0r"));</v>
+        <v>17</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4:F8" si="0">"Assert.IsFalse(ServicioContrasenas.EsValida("""&amp;C4&amp;"""));"</f>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida("ClaveSegu1!"));</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -540,17 +550,17 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C5 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("p@ssw0rd"));</v>
+        <v>19</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida("clavesegur1!"));</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -558,17 +568,17 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C6 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("P@SSW0RD"));</v>
+        <v>21</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida("CLAVESEGUR1!"));</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -576,17 +586,17 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C7 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("P@ssword"));</v>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida("ClaveSegura!"));</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -594,17 +604,17 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f>+"Assert.IsFalse(ServicioContrasenas.EsValida(""" &amp; C8 &amp; """));"</f>
-        <v>Assert.IsFalse(ServicioContrasenas.EsValida("Passw0rd"));</v>
+        <v>25</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida("ClaveSegur12"));</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -612,27 +622,58 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="1" t="str">
-        <f>+"Assert.IsTrue(ServicioContrasenas.EsValida(""" &amp; C9 &amp; """));"</f>
-        <v>Assert.IsTrue(ServicioContrasenas.EsValida("P@ssw0rd"));</v>
+        <v>27</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <f>"Assert.IsTrue(ServicioContrasenas.EsValida("""&amp;C9&amp;"""));"</f>
+        <v>Assert.IsTrue(ServicioContrasenas.EsValida("ClaveSegur1!"));</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="str">
+        <f>"Assert.IsFalse(ServicioContrasenas.EsValida(string.Empty));"</f>
+        <v>Assert.IsFalse(ServicioContrasenas.EsValida(string.Empty));</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <f>"Assert.IsTrue(ServicioContrasenas.EsValida("""&amp;C11&amp;"""));"</f>
+        <v>Assert.IsTrue(ServicioContrasenas.EsValida("ClaveSegur12!"));</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{972217D2-A335-4328-A955-131D198E9EC3}"/>
-    <hyperlink ref="C5" r:id="rId2" xr:uid="{C68A3E60-1211-4490-9E29-D59EE4DD5EE1}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{67771205-44AB-4277-86C4-F9532086649E}"/>
-    <hyperlink ref="C7" r:id="rId4" xr:uid="{6D2E3526-3EAC-4C3F-9C8E-3D7DC8F6004E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>